--- a/healthcare_surveys/050_hospital_community_relations_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/050_hospital_community_relations_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'service_1'}</t>
+          <t>service_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Service 1'}</t>
+          <t>Service 1</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'service_2'}</t>
+          <t>service_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Service 2'}</t>
+          <t>Service 2</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'service_3'}</t>
+          <t>service_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Service 3'}</t>
+          <t>Service 3</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'service_4'}</t>
+          <t>service_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Service 4'}</t>
+          <t>Service 4</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'service_5'}</t>
+          <t>service_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Service 5'}</t>
+          <t>Service 5</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'newsletter'}</t>
+          <t>newsletter</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Newsletter'}</t>
+          <t>Newsletter</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'text_message'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Text Message'}</t>
+          <t>Text Message</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree nor Disagree'}</t>
+          <t>Neither Agree nor Disagree</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
